--- a/colombres/JULIO/JULIO COLOMBRES 360.xlsx
+++ b/colombres/JULIO/JULIO COLOMBRES 360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\JULIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F28307-488F-47EE-969A-C199053A1B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D811B4C-EDEF-4A76-BD11-BE3973EFDCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="176">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>PREVISION ORDINARIA - ARREGLOS DE ASCENSOR QUE SE HICIERON - BOMBAS (QUE SE DEBEN ABONAR EN LOS PRIMEROS DIAS)</t>
+  </si>
+  <si>
+    <t>EL DEPOSITO DEL MES PASADO DE 545.000 ES DE EL</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1182,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1380,6 +1383,39 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1404,38 +1440,47 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1449,48 +1494,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1883,68 +1887,68 @@
       <c r="D3" s="129"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="156" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="158"/>
+      <c r="B4" s="156"/>
       <c r="C4" s="130"/>
       <c r="D4" s="130"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="158"/>
-      <c r="B5" s="158"/>
+      <c r="A5" s="156"/>
+      <c r="B5" s="156"/>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="158"/>
-      <c r="B6" s="158"/>
+      <c r="A6" s="156"/>
+      <c r="B6" s="156"/>
       <c r="C6" s="130"/>
       <c r="D6" s="130"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="158"/>
-      <c r="B7" s="158"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="156"/>
       <c r="C7" s="130"/>
       <c r="D7" s="130"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="157" t="s">
+      <c r="B9" s="153" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="157"/>
+      <c r="B10" s="153"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="157"/>
+      <c r="B11" s="153"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="152" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="156"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
+      <c r="A15" s="152"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="156"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
+      <c r="A16" s="152"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="156"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
+      <c r="A17" s="152"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2345,10 +2349,10 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="159" t="s">
+      <c r="A58" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="160"/>
+      <c r="B58" s="147"/>
       <c r="C58" s="111"/>
       <c r="D58" s="96"/>
     </row>
@@ -2380,34 +2384,34 @@
       <c r="D61" s="94"/>
     </row>
     <row r="62" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="161" t="s">
+      <c r="A62" s="148" t="s">
         <v>132</v>
       </c>
-      <c r="B62" s="162"/>
+      <c r="B62" s="149"/>
       <c r="C62" s="111"/>
       <c r="D62" s="115"/>
     </row>
     <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="161" t="s">
+      <c r="A63" s="148" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="162"/>
+      <c r="B63" s="149"/>
       <c r="C63" s="111"/>
       <c r="D63" s="114"/>
     </row>
     <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="163" t="s">
+      <c r="A64" s="150" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="164"/>
+      <c r="B64" s="151"/>
       <c r="C64" s="31"/>
       <c r="D64" s="93"/>
     </row>
     <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="146" t="s">
+      <c r="A65" s="157" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="147"/>
+      <c r="B65" s="158"/>
       <c r="C65" s="31">
         <v>250000</v>
       </c>
@@ -2416,10 +2420,10 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="146" t="s">
+      <c r="A66" s="157" t="s">
         <v>157</v>
       </c>
-      <c r="B66" s="147"/>
+      <c r="B66" s="158"/>
       <c r="C66" s="31">
         <v>33429</v>
       </c>
@@ -2428,10 +2432,10 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="146" t="s">
+      <c r="A67" s="157" t="s">
         <v>159</v>
       </c>
-      <c r="B67" s="147"/>
+      <c r="B67" s="158"/>
       <c r="C67" s="31">
         <v>70000</v>
       </c>
@@ -2440,10 +2444,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="146" t="s">
+      <c r="A68" s="157" t="s">
         <v>155</v>
       </c>
-      <c r="B68" s="147"/>
+      <c r="B68" s="158"/>
       <c r="C68" s="31">
         <v>191330</v>
       </c>
@@ -2508,11 +2512,11 @@
       <c r="D74" s="101"/>
     </row>
     <row r="75" spans="1:6" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="148" t="s">
+      <c r="A75" s="159" t="s">
         <v>174</v>
       </c>
-      <c r="B75" s="149"/>
-      <c r="C75" s="150"/>
+      <c r="B75" s="160"/>
+      <c r="C75" s="161"/>
       <c r="D75" s="102">
         <v>2334921.91</v>
       </c>
@@ -2642,22 +2646,22 @@
     <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="153"/>
-      <c r="B97" s="153"/>
-      <c r="C97" s="153"/>
-      <c r="D97" s="153"/>
+      <c r="A97" s="164"/>
+      <c r="B97" s="164"/>
+      <c r="C97" s="164"/>
+      <c r="D97" s="164"/>
     </row>
     <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="153"/>
-      <c r="B98" s="153"/>
-      <c r="C98" s="153"/>
-      <c r="D98" s="153"/>
+      <c r="A98" s="164"/>
+      <c r="B98" s="164"/>
+      <c r="C98" s="164"/>
+      <c r="D98" s="164"/>
     </row>
     <row r="99" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="153"/>
-      <c r="B99" s="153"/>
-      <c r="C99" s="153"/>
-      <c r="D99" s="153"/>
+      <c r="A99" s="164"/>
+      <c r="B99" s="164"/>
+      <c r="C99" s="164"/>
+      <c r="D99" s="164"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
@@ -2739,14 +2743,14 @@
       <c r="C110" s="41"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="152" t="s">
+      <c r="A112" s="163" t="s">
         <v>78</v>
       </c>
-      <c r="B112" s="152"/>
+      <c r="B112" s="163"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="152"/>
-      <c r="B113" s="152"/>
+      <c r="A113" s="163"/>
+      <c r="B113" s="163"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="109" t="s">
@@ -2809,36 +2813,37 @@
       <c r="L121" s="8"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="151"/>
-      <c r="B122" s="151"/>
-      <c r="C122" s="151"/>
-      <c r="D122" s="151"/>
+      <c r="A122" s="162"/>
+      <c r="B122" s="162"/>
+      <c r="C122" s="162"/>
+      <c r="D122" s="162"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="151"/>
-      <c r="B123" s="151"/>
-      <c r="C123" s="151"/>
-      <c r="D123" s="151"/>
+      <c r="A123" s="162"/>
+      <c r="B123" s="162"/>
+      <c r="C123" s="162"/>
+      <c r="D123" s="162"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="151"/>
-      <c r="B124" s="151"/>
-      <c r="C124" s="151"/>
-      <c r="D124" s="151"/>
+      <c r="A124" s="162"/>
+      <c r="B124" s="162"/>
+      <c r="C124" s="162"/>
+      <c r="D124" s="162"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="151"/>
-      <c r="B125" s="151"/>
-      <c r="C125" s="151"/>
-      <c r="D125" s="151"/>
+      <c r="A125" s="162"/>
+      <c r="B125" s="162"/>
+      <c r="C125" s="162"/>
+      <c r="D125" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A122:D125"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A97:D99"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A4:B7"/>
@@ -2846,13 +2851,12 @@
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A122:D125"/>
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A97:D99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A14:D17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2888,18 +2892,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="171" t="s">
+      <c r="B1" s="165" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2908,16 +2912,16 @@
     </row>
     <row r="2" spans="1:19" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2931,16 +2935,16 @@
     </row>
     <row r="3" spans="1:19" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2950,10 +2954,10 @@
       <c r="P3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="165" t="s">
+      <c r="A4" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="181" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="169" t="s">
@@ -2977,49 +2981,49 @@
       <c r="I4" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="J4" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="176" t="s">
+      <c r="K4" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="176" t="s">
+      <c r="L4" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="176" t="s">
+      <c r="M4" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="N4" s="177" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="173" t="s">
+      <c r="P4" s="167" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="41"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="166"/>
-      <c r="B5" s="168"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="182"/>
+      <c r="A5" s="180"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="178"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="174"/>
+      <c r="P5" s="168"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3367,10 +3371,10 @@
       <c r="B12" s="57">
         <v>7</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="183" t="s">
         <v>101</v>
       </c>
       <c r="E12" s="57"/>
@@ -3414,6 +3418,9 @@
       <c r="Q12" s="41">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S12" s="113" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4653,91 +4660,96 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="151"/>
-      <c r="E37" s="151"/>
-      <c r="F37" s="151"/>
-      <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
-      <c r="I37" s="151"/>
-      <c r="J37" s="151"/>
-      <c r="K37" s="151"/>
-      <c r="L37" s="151"/>
-      <c r="M37" s="151"/>
-      <c r="N37" s="151"/>
-      <c r="O37" s="151"/>
+      <c r="D37" s="162"/>
+      <c r="E37" s="162"/>
+      <c r="F37" s="162"/>
+      <c r="G37" s="162"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="162"/>
+      <c r="K37" s="162"/>
+      <c r="L37" s="162"/>
+      <c r="M37" s="162"/>
+      <c r="N37" s="162"/>
+      <c r="O37" s="162"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="151"/>
-      <c r="E38" s="151"/>
-      <c r="F38" s="151"/>
-      <c r="G38" s="151"/>
-      <c r="H38" s="151"/>
-      <c r="I38" s="151"/>
-      <c r="J38" s="151"/>
-      <c r="K38" s="151"/>
-      <c r="L38" s="151"/>
-      <c r="M38" s="151"/>
-      <c r="N38" s="151"/>
-      <c r="O38" s="151"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="162"/>
+      <c r="L38" s="162"/>
+      <c r="M38" s="162"/>
+      <c r="N38" s="162"/>
+      <c r="O38" s="162"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
-      <c r="G39" s="151"/>
-      <c r="H39" s="151"/>
-      <c r="I39" s="151"/>
-      <c r="J39" s="151"/>
-      <c r="K39" s="151"/>
-      <c r="L39" s="151"/>
-      <c r="M39" s="151"/>
-      <c r="N39" s="151"/>
-      <c r="O39" s="151"/>
+      <c r="D39" s="162"/>
+      <c r="E39" s="162"/>
+      <c r="F39" s="162"/>
+      <c r="G39" s="162"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+      <c r="M39" s="162"/>
+      <c r="N39" s="162"/>
+      <c r="O39" s="162"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="151"/>
-      <c r="E40" s="151"/>
-      <c r="F40" s="151"/>
-      <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
-      <c r="I40" s="151"/>
-      <c r="J40" s="151"/>
-      <c r="K40" s="151"/>
-      <c r="L40" s="151"/>
-      <c r="M40" s="151"/>
-      <c r="N40" s="151"/>
-      <c r="O40" s="151"/>
+      <c r="D40" s="162"/>
+      <c r="E40" s="162"/>
+      <c r="F40" s="162"/>
+      <c r="G40" s="162"/>
+      <c r="H40" s="162"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="162"/>
+      <c r="K40" s="162"/>
+      <c r="L40" s="162"/>
+      <c r="M40" s="162"/>
+      <c r="N40" s="162"/>
+      <c r="O40" s="162"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="151"/>
-      <c r="E41" s="151"/>
-      <c r="F41" s="151"/>
-      <c r="G41" s="151"/>
-      <c r="H41" s="151"/>
-      <c r="I41" s="151"/>
-      <c r="J41" s="151"/>
-      <c r="K41" s="151"/>
-      <c r="L41" s="151"/>
-      <c r="M41" s="151"/>
-      <c r="N41" s="151"/>
-      <c r="O41" s="151"/>
+      <c r="D41" s="162"/>
+      <c r="E41" s="162"/>
+      <c r="F41" s="162"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="162"/>
+      <c r="N41" s="162"/>
+      <c r="O41" s="162"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="151"/>
-      <c r="E42" s="151"/>
-      <c r="F42" s="151"/>
-      <c r="G42" s="151"/>
-      <c r="H42" s="151"/>
-      <c r="I42" s="151"/>
-      <c r="J42" s="151"/>
-      <c r="K42" s="151"/>
-      <c r="L42" s="151"/>
-      <c r="M42" s="151"/>
-      <c r="N42" s="151"/>
-      <c r="O42" s="151"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="162"/>
+      <c r="K42" s="162"/>
+      <c r="L42" s="162"/>
+      <c r="M42" s="162"/>
+      <c r="N42" s="162"/>
+      <c r="O42" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4750,11 +4762,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/JULIO/JULIO COLOMBRES 360.xlsx
+++ b/colombres/JULIO/JULIO COLOMBRES 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\JULIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D811B4C-EDEF-4A76-BD11-BE3973EFDCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A901B0F-4BBA-43C4-B76F-EA6CBB67C009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1383,6 +1383,43 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1404,41 +1441,23 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1452,9 +1471,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1464,9 +1480,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1482,19 +1495,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1913,42 +1913,42 @@
       <c r="D7" s="130"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="155" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="153"/>
+      <c r="B10" s="155"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="153"/>
+      <c r="B11" s="155"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="165" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
+      <c r="B14" s="165"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="152"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
+      <c r="A15" s="165"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="165"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="152"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
+      <c r="A16" s="165"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="152"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
+      <c r="A17" s="165"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2200,10 +2200,10 @@
       <c r="D44" s="61"/>
     </row>
     <row r="45" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="154" t="s">
+      <c r="A45" s="153" t="s">
         <v>136</v>
       </c>
-      <c r="B45" s="155"/>
+      <c r="B45" s="154"/>
       <c r="C45" s="144">
         <v>175052</v>
       </c>
@@ -2212,10 +2212,10 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="154" t="s">
+      <c r="A46" s="153" t="s">
         <v>137</v>
       </c>
-      <c r="B46" s="155"/>
+      <c r="B46" s="154"/>
       <c r="C46" s="145">
         <v>4203</v>
       </c>
@@ -2349,10 +2349,10 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="146" t="s">
+      <c r="A58" s="159" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="147"/>
+      <c r="B58" s="160"/>
       <c r="C58" s="111"/>
       <c r="D58" s="96"/>
     </row>
@@ -2384,26 +2384,26 @@
       <c r="D61" s="94"/>
     </row>
     <row r="62" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="148" t="s">
+      <c r="A62" s="161" t="s">
         <v>132</v>
       </c>
-      <c r="B62" s="149"/>
+      <c r="B62" s="162"/>
       <c r="C62" s="111"/>
       <c r="D62" s="115"/>
     </row>
     <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="148" t="s">
+      <c r="A63" s="161" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="149"/>
+      <c r="B63" s="162"/>
       <c r="C63" s="111"/>
       <c r="D63" s="114"/>
     </row>
     <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="150" t="s">
+      <c r="A64" s="163" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="151"/>
+      <c r="B64" s="164"/>
       <c r="C64" s="31"/>
       <c r="D64" s="93"/>
     </row>
@@ -2512,11 +2512,11 @@
       <c r="D74" s="101"/>
     </row>
     <row r="75" spans="1:6" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="159" t="s">
+      <c r="A75" s="147" t="s">
         <v>174</v>
       </c>
-      <c r="B75" s="160"/>
-      <c r="C75" s="161"/>
+      <c r="B75" s="148"/>
+      <c r="C75" s="149"/>
       <c r="D75" s="102">
         <v>2334921.91</v>
       </c>
@@ -2557,14 +2557,14 @@
       <c r="D80" s="108"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="154"/>
-      <c r="B81" s="155"/>
+      <c r="A81" s="153"/>
+      <c r="B81" s="154"/>
       <c r="C81" s="95"/>
       <c r="D81" s="92"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="154"/>
-      <c r="B82" s="155"/>
+      <c r="A82" s="153"/>
+      <c r="B82" s="154"/>
       <c r="C82" s="95"/>
       <c r="D82" s="92"/>
     </row>
@@ -2646,22 +2646,22 @@
     <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="164"/>
-      <c r="B97" s="164"/>
-      <c r="C97" s="164"/>
-      <c r="D97" s="164"/>
+      <c r="A97" s="152"/>
+      <c r="B97" s="152"/>
+      <c r="C97" s="152"/>
+      <c r="D97" s="152"/>
     </row>
     <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="164"/>
-      <c r="B98" s="164"/>
-      <c r="C98" s="164"/>
-      <c r="D98" s="164"/>
+      <c r="A98" s="152"/>
+      <c r="B98" s="152"/>
+      <c r="C98" s="152"/>
+      <c r="D98" s="152"/>
     </row>
     <row r="99" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="164"/>
-      <c r="B99" s="164"/>
-      <c r="C99" s="164"/>
-      <c r="D99" s="164"/>
+      <c r="A99" s="152"/>
+      <c r="B99" s="152"/>
+      <c r="C99" s="152"/>
+      <c r="D99" s="152"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
@@ -2743,14 +2743,14 @@
       <c r="C110" s="41"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="163" t="s">
+      <c r="A112" s="151" t="s">
         <v>78</v>
       </c>
-      <c r="B112" s="163"/>
+      <c r="B112" s="151"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="163"/>
-      <c r="B113" s="163"/>
+      <c r="A113" s="151"/>
+      <c r="B113" s="151"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="109" t="s">
@@ -2813,37 +2813,31 @@
       <c r="L121" s="8"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="162"/>
-      <c r="B122" s="162"/>
-      <c r="C122" s="162"/>
-      <c r="D122" s="162"/>
+      <c r="A122" s="150"/>
+      <c r="B122" s="150"/>
+      <c r="C122" s="150"/>
+      <c r="D122" s="150"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="162"/>
-      <c r="B123" s="162"/>
-      <c r="C123" s="162"/>
-      <c r="D123" s="162"/>
+      <c r="A123" s="150"/>
+      <c r="B123" s="150"/>
+      <c r="C123" s="150"/>
+      <c r="D123" s="150"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="162"/>
-      <c r="B124" s="162"/>
-      <c r="C124" s="162"/>
-      <c r="D124" s="162"/>
+      <c r="A124" s="150"/>
+      <c r="B124" s="150"/>
+      <c r="C124" s="150"/>
+      <c r="D124" s="150"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="162"/>
-      <c r="B125" s="162"/>
-      <c r="C125" s="162"/>
-      <c r="D125" s="162"/>
+      <c r="A125" s="150"/>
+      <c r="B125" s="150"/>
+      <c r="C125" s="150"/>
+      <c r="D125" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A122:D125"/>
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A97:D99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A4:B7"/>
@@ -2857,6 +2851,12 @@
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A122:D125"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A97:D99"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2892,18 +2892,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="172" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="172"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2912,16 +2912,16 @@
     </row>
     <row r="2" spans="1:19" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2935,16 +2935,16 @@
     </row>
     <row r="3" spans="1:19" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2954,76 +2954,76 @@
       <c r="P3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="166" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="169" t="s">
+      <c r="C4" s="170" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="169" t="s">
+      <c r="D4" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="169" t="s">
+      <c r="E4" s="170" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="169" t="s">
+      <c r="F4" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="169" t="s">
+      <c r="G4" s="170" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="169" t="s">
+      <c r="H4" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="169" t="s">
+      <c r="I4" s="170" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="174" t="s">
+      <c r="J4" s="179" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="171" t="s">
+      <c r="K4" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="171" t="s">
+      <c r="L4" s="177" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="171" t="s">
+      <c r="M4" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="177" t="s">
+      <c r="N4" s="182" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="167" t="s">
+      <c r="P4" s="174" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="41"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="180"/>
-      <c r="B5" s="182"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="170"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="178"/>
+      <c r="A5" s="167"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="178"/>
+      <c r="L5" s="181"/>
+      <c r="M5" s="178"/>
+      <c r="N5" s="183"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="168"/>
+      <c r="P5" s="175"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3371,10 +3371,10 @@
       <c r="B12" s="57">
         <v>7</v>
       </c>
-      <c r="C12" s="183" t="s">
+      <c r="C12" s="146" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="183" t="s">
+      <c r="D12" s="146" t="s">
         <v>101</v>
       </c>
       <c r="E12" s="57"/>
@@ -4660,96 +4660,91 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="162"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="162"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
-      <c r="K37" s="162"/>
-      <c r="L37" s="162"/>
-      <c r="M37" s="162"/>
-      <c r="N37" s="162"/>
-      <c r="O37" s="162"/>
+      <c r="D37" s="150"/>
+      <c r="E37" s="150"/>
+      <c r="F37" s="150"/>
+      <c r="G37" s="150"/>
+      <c r="H37" s="150"/>
+      <c r="I37" s="150"/>
+      <c r="J37" s="150"/>
+      <c r="K37" s="150"/>
+      <c r="L37" s="150"/>
+      <c r="M37" s="150"/>
+      <c r="N37" s="150"/>
+      <c r="O37" s="150"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="162"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="162"/>
-      <c r="L38" s="162"/>
-      <c r="M38" s="162"/>
-      <c r="N38" s="162"/>
-      <c r="O38" s="162"/>
+      <c r="D38" s="150"/>
+      <c r="E38" s="150"/>
+      <c r="F38" s="150"/>
+      <c r="G38" s="150"/>
+      <c r="H38" s="150"/>
+      <c r="I38" s="150"/>
+      <c r="J38" s="150"/>
+      <c r="K38" s="150"/>
+      <c r="L38" s="150"/>
+      <c r="M38" s="150"/>
+      <c r="N38" s="150"/>
+      <c r="O38" s="150"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="162"/>
-      <c r="E39" s="162"/>
-      <c r="F39" s="162"/>
-      <c r="G39" s="162"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="162"/>
-      <c r="K39" s="162"/>
-      <c r="L39" s="162"/>
-      <c r="M39" s="162"/>
-      <c r="N39" s="162"/>
-      <c r="O39" s="162"/>
+      <c r="D39" s="150"/>
+      <c r="E39" s="150"/>
+      <c r="F39" s="150"/>
+      <c r="G39" s="150"/>
+      <c r="H39" s="150"/>
+      <c r="I39" s="150"/>
+      <c r="J39" s="150"/>
+      <c r="K39" s="150"/>
+      <c r="L39" s="150"/>
+      <c r="M39" s="150"/>
+      <c r="N39" s="150"/>
+      <c r="O39" s="150"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="162"/>
-      <c r="E40" s="162"/>
-      <c r="F40" s="162"/>
-      <c r="G40" s="162"/>
-      <c r="H40" s="162"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="162"/>
-      <c r="K40" s="162"/>
-      <c r="L40" s="162"/>
-      <c r="M40" s="162"/>
-      <c r="N40" s="162"/>
-      <c r="O40" s="162"/>
+      <c r="D40" s="150"/>
+      <c r="E40" s="150"/>
+      <c r="F40" s="150"/>
+      <c r="G40" s="150"/>
+      <c r="H40" s="150"/>
+      <c r="I40" s="150"/>
+      <c r="J40" s="150"/>
+      <c r="K40" s="150"/>
+      <c r="L40" s="150"/>
+      <c r="M40" s="150"/>
+      <c r="N40" s="150"/>
+      <c r="O40" s="150"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="162"/>
-      <c r="E41" s="162"/>
-      <c r="F41" s="162"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="162"/>
-      <c r="N41" s="162"/>
-      <c r="O41" s="162"/>
+      <c r="D41" s="150"/>
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="150"/>
+      <c r="J41" s="150"/>
+      <c r="K41" s="150"/>
+      <c r="L41" s="150"/>
+      <c r="M41" s="150"/>
+      <c r="N41" s="150"/>
+      <c r="O41" s="150"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="162"/>
-      <c r="E42" s="162"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="162"/>
-      <c r="I42" s="162"/>
-      <c r="J42" s="162"/>
-      <c r="K42" s="162"/>
-      <c r="L42" s="162"/>
-      <c r="M42" s="162"/>
-      <c r="N42" s="162"/>
-      <c r="O42" s="162"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+      <c r="I42" s="150"/>
+      <c r="J42" s="150"/>
+      <c r="K42" s="150"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="150"/>
+      <c r="O42" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4762,6 +4757,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
